--- a/youzi/华鑫宁波分/index.xlsx
+++ b/youzi/华鑫宁波分/index.xlsx
@@ -39,19 +39,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE3626E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,7 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
+        <fgColor rgb="FFAD1F2D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,31 +117,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,55 +327,199 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,54 +531,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -231,343 +549,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="10" t="str">
         <v>净卖: -1841.46万</v>
       </c>
       <c r="E2">
@@ -1833,40 +1833,40 @@
       <c r="H2">
         <v>0.21</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="6">
         <v>9.78</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="8">
         <v>4.55</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="2">
         <v>10.25</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="11">
         <v>8.54</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="12">
         <v>9.42</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="3">
         <v>3.67</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="9">
         <v>3.88</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="13">
         <v>3.73</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>2.95</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="7">
         <v>3.26</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="4">
         <v>0.88</v>
       </c>
-      <c r="T2" s="7">
+      <c r="T2" s="5">
         <v>32.61</v>
       </c>
     </row>
@@ -1895,40 +1895,40 @@
       <c r="H3">
         <v>3.56</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="15">
         <v>6.22</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="19">
         <v>5.86</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="20">
         <v>4.44</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="23">
         <v>4.95</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="16">
         <v>1.33</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="25">
         <v>0.83</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="21">
         <v>3.23</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="24">
         <v>3.88</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="17">
         <v>1.66</v>
       </c>
       <c r="R3" s="26">
         <v>1.05</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="22">
         <v>2.73</v>
       </c>
-      <c r="T3" s="22">
+      <c r="T3" s="18">
         <v>136.02</v>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>001209</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="37" t="str">
         <v>净买: 927.43万</v>
       </c>
       <c r="E4">
@@ -1957,40 +1957,40 @@
       <c r="H4">
         <v>-0.96</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="33">
         <v>11.08</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="38">
         <v>22.21</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="29">
         <v>34.45</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="39">
         <v>21.05</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="27">
         <v>8.95</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="30">
         <v>4.17</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="28">
         <v>0.7</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="31">
         <v>1.99</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="34">
         <v>-0.46</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="32">
         <v>-1.99</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="35">
         <v>-2.46</v>
       </c>
-      <c r="T4" s="39">
+      <c r="T4" s="36">
         <v>-5.19</v>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>001277</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="48" t="str">
         <v>净卖: -115.58万</v>
       </c>
       <c r="E5">
@@ -2019,40 +2019,40 @@
       <c r="H5">
         <v>4.64</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="49">
         <v>5.12</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="50">
         <v>-5.38</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="45">
         <v>-9.79</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="51">
         <v>-8.54</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="42">
         <v>-12.18</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="46">
         <v>-15.6</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="41">
         <v>-18.85</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="47">
         <v>-17.8</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="43">
         <v>-17.2</v>
       </c>
       <c r="R5" s="44">
         <v>-18.47</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="52">
         <v>-17.05</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="40">
         <v>-23.81</v>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>002865</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="60" t="str">
         <v>净买: 1604.62万</v>
       </c>
       <c r="E6">
@@ -2081,28 +2081,28 @@
       <c r="H6">
         <v>-9.87</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="53">
         <v>-0.15</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="54">
         <v>-5.03</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="61">
         <v>-5.69</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="63">
         <v>-4.56</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="55">
         <v>-6.32</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="59">
         <v>-9.04</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="56">
         <v>-13.12</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="62">
         <v>-16.35</v>
       </c>
       <c r="Q6" s="64">
@@ -2111,10 +2111,10 @@
       <c r="R6" s="65">
         <v>-17.98</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="57">
         <v>-9.78</v>
       </c>
-      <c r="T6" s="55">
+      <c r="T6" s="58">
         <v>-27.88</v>
       </c>
     </row>
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="76">
+      <c r="I8" s="75">
         <v>80</v>
       </c>
-      <c r="J8" s="67">
+      <c r="J8" s="70">
         <v>60</v>
       </c>
-      <c r="K8" s="68">
+      <c r="K8" s="71">
         <v>60</v>
       </c>
-      <c r="L8" s="71">
+      <c r="L8" s="76">
         <v>60</v>
       </c>
-      <c r="M8" s="73">
+      <c r="M8" s="77">
         <v>60</v>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="66">
         <v>60</v>
       </c>
-      <c r="O8" s="69">
+      <c r="O8" s="72">
         <v>60</v>
       </c>
-      <c r="P8" s="74">
+      <c r="P8" s="67">
         <v>60</v>
       </c>
-      <c r="Q8" s="75">
+      <c r="Q8" s="74">
         <v>40</v>
       </c>
-      <c r="R8" s="77">
+      <c r="R8" s="73">
         <v>40</v>
       </c>
-      <c r="S8" s="70">
+      <c r="S8" s="68">
         <v>40</v>
       </c>
-      <c r="T8" s="66">
+      <c r="T8" s="69">
         <v>40</v>
       </c>
     </row>
@@ -2225,40 +2225,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="85">
+      <c r="I9" s="82">
         <v>6.41</v>
       </c>
-      <c r="J9" s="80">
+      <c r="J9" s="85">
         <v>4.44</v>
       </c>
-      <c r="K9" s="81">
+      <c r="K9" s="89">
         <v>6.73</v>
       </c>
-      <c r="L9" s="82">
+      <c r="L9" s="83">
         <v>4.29</v>
       </c>
-      <c r="M9" s="86">
+      <c r="M9" s="78">
         <v>0.24</v>
       </c>
-      <c r="N9" s="89">
+      <c r="N9" s="86">
         <v>-3.19</v>
       </c>
-      <c r="O9" s="83">
+      <c r="O9" s="87">
         <v>-4.83</v>
       </c>
-      <c r="P9" s="78">
+      <c r="P9" s="88">
         <v>-4.91</v>
       </c>
-      <c r="Q9" s="87">
+      <c r="Q9" s="79">
         <v>-5.88</v>
       </c>
-      <c r="R9" s="79">
+      <c r="R9" s="80">
         <v>-6.83</v>
       </c>
-      <c r="S9" s="84">
+      <c r="S9" s="81">
         <v>-5.14</v>
       </c>
-      <c r="T9" s="88">
+      <c r="T9" s="84">
         <v>22.35</v>
       </c>
     </row>

--- a/youzi/华鑫宁波分/index.xlsx
+++ b/youzi/华鑫宁波分/index.xlsx
@@ -39,25 +39,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEA8791"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,25 +219,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,19 +309,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,19 +441,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,61 +453,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,49 +543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -268,300 +562,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="13" t="str">
         <v>净卖: -1841.46万</v>
       </c>
       <c r="E2">
@@ -1833,40 +1833,40 @@
       <c r="H2">
         <v>0.21</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="7">
         <v>9.78</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="1">
         <v>4.55</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="5">
         <v>10.25</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="8">
         <v>8.54</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="9">
         <v>9.42</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="11">
         <v>3.67</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="6">
         <v>3.88</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="12">
         <v>3.73</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="10">
         <v>2.95</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="2">
         <v>3.26</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="3">
         <v>0.88</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="4">
         <v>32.61</v>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002281</v>
       </c>
-      <c r="D3" s="14" t="str">
+      <c r="D3" s="25" t="str">
         <v>净卖: -4437.11万</v>
       </c>
       <c r="E3">
@@ -1895,37 +1895,37 @@
       <c r="H3">
         <v>3.56</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="19">
         <v>6.22</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="20">
         <v>5.86</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="21">
         <v>4.44</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="22">
         <v>4.95</v>
       </c>
       <c r="M3" s="16">
         <v>1.33</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="26">
         <v>0.83</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="14">
         <v>3.23</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="23">
         <v>3.88</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="15">
         <v>1.66</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="24">
         <v>1.05</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="17">
         <v>2.73</v>
       </c>
       <c r="T3" s="18">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>001209</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="27" t="str">
         <v>净买: 927.43万</v>
       </c>
       <c r="E4">
@@ -1960,37 +1960,37 @@
       <c r="I4" s="33">
         <v>11.08</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="37">
         <v>22.21</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="38">
         <v>34.45</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="30">
         <v>21.05</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="31">
         <v>8.95</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="34">
         <v>4.17</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="35">
         <v>0.7</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="32">
         <v>1.99</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="28">
         <v>-0.46</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="36">
         <v>-1.99</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="29">
         <v>-2.46</v>
       </c>
-      <c r="T4" s="36">
+      <c r="T4" s="39">
         <v>-5.19</v>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>001277</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="45" t="str">
         <v>净卖: -115.58万</v>
       </c>
       <c r="E5">
@@ -2025,34 +2025,34 @@
       <c r="J5" s="50">
         <v>-5.38</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="41">
         <v>-9.79</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="48">
         <v>-8.54</v>
       </c>
       <c r="M5" s="42">
         <v>-12.18</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="51">
         <v>-15.6</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="46">
         <v>-18.85</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="43">
         <v>-17.8</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="52">
         <v>-17.2</v>
       </c>
       <c r="R5" s="44">
         <v>-18.47</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="40">
         <v>-17.05</v>
       </c>
-      <c r="T5" s="40">
+      <c r="T5" s="47">
         <v>-23.81</v>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>002865</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="59" t="str">
         <v>净买: 1604.62万</v>
       </c>
       <c r="E6">
@@ -2081,40 +2081,40 @@
       <c r="H6">
         <v>-9.87</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="64">
         <v>-0.15</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="65">
         <v>-5.03</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="60">
         <v>-5.69</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="61">
         <v>-4.56</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="58">
         <v>-6.32</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="62">
         <v>-9.04</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="55">
         <v>-13.12</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="56">
         <v>-16.35</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="63">
         <v>-16.35</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="53">
         <v>-17.98</v>
       </c>
       <c r="S6" s="57">
         <v>-9.78</v>
       </c>
-      <c r="T6" s="58">
+      <c r="T6" s="54">
         <v>-27.88</v>
       </c>
     </row>
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="75">
+      <c r="I8" s="69">
         <v>80</v>
       </c>
       <c r="J8" s="70">
         <v>60</v>
       </c>
-      <c r="K8" s="71">
+      <c r="K8" s="73">
         <v>60</v>
       </c>
-      <c r="L8" s="76">
+      <c r="L8" s="71">
         <v>60</v>
       </c>
-      <c r="M8" s="77">
+      <c r="M8" s="74">
         <v>60</v>
       </c>
-      <c r="N8" s="66">
+      <c r="N8" s="72">
         <v>60</v>
       </c>
-      <c r="O8" s="72">
+      <c r="O8" s="75">
         <v>60</v>
       </c>
-      <c r="P8" s="67">
+      <c r="P8" s="66">
         <v>60</v>
       </c>
-      <c r="Q8" s="74">
+      <c r="Q8" s="67">
         <v>40</v>
       </c>
-      <c r="R8" s="73">
+      <c r="R8" s="68">
         <v>40</v>
       </c>
-      <c r="S8" s="68">
+      <c r="S8" s="76">
         <v>40</v>
       </c>
-      <c r="T8" s="69">
+      <c r="T8" s="77">
         <v>40</v>
       </c>
     </row>
@@ -2225,40 +2225,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="82">
+      <c r="I9" s="84">
         <v>6.41</v>
       </c>
-      <c r="J9" s="85">
+      <c r="J9" s="88">
         <v>4.44</v>
       </c>
       <c r="K9" s="89">
         <v>6.73</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="85">
         <v>4.29</v>
       </c>
       <c r="M9" s="78">
         <v>0.24</v>
       </c>
-      <c r="N9" s="86">
+      <c r="N9" s="79">
         <v>-3.19</v>
       </c>
-      <c r="O9" s="87">
+      <c r="O9" s="86">
         <v>-4.83</v>
       </c>
-      <c r="P9" s="88">
+      <c r="P9" s="80">
         <v>-4.91</v>
       </c>
-      <c r="Q9" s="79">
+      <c r="Q9" s="82">
         <v>-5.88</v>
       </c>
-      <c r="R9" s="80">
+      <c r="R9" s="81">
         <v>-6.83</v>
       </c>
-      <c r="S9" s="81">
+      <c r="S9" s="83">
         <v>-5.14</v>
       </c>
-      <c r="T9" s="84">
+      <c r="T9" s="87">
         <v>22.35</v>
       </c>
     </row>

--- a/youzi/华鑫宁波分/index.xlsx
+++ b/youzi/华鑫宁波分/index.xlsx
@@ -39,13 +39,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDF4755"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
+        <fgColor rgb="FFAD1F2D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,55 +87,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE3626E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,13 +171,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,7 +195,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
+        <fgColor rgb="FF41B15B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,37 +207,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,7 +309,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,31 +429,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,19 +525,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,307 +543,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>0.21</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="9">
         <v>9.78</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="6">
         <v>4.55</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="1">
         <v>10.25</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="10">
         <v>8.54</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="7">
         <v>9.42</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="2">
         <v>3.67</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="3">
         <v>3.88</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="11">
         <v>3.73</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="4">
         <v>2.95</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="5">
         <v>3.26</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="8">
         <v>0.88</v>
       </c>
-      <c r="T2" s="4">
-        <v>32.61</v>
+      <c r="T2" s="12">
+        <v>35.61</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002281</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="22" t="str">
         <v>净卖: -4437.11万</v>
       </c>
       <c r="E3">
@@ -1895,41 +1895,41 @@
       <c r="H3">
         <v>3.56</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="21">
         <v>6.22</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="23">
         <v>5.86</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="24">
         <v>4.44</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="25">
         <v>4.95</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="26">
         <v>1.33</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="15">
         <v>0.83</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="16">
         <v>3.23</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="18">
         <v>3.88</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="17">
         <v>1.66</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="19">
         <v>1.05</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="20">
         <v>2.73</v>
       </c>
-      <c r="T3" s="18">
-        <v>136.02</v>
+      <c r="T3" s="14">
+        <v>142.53</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>001209</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 927.43万</v>
       </c>
       <c r="E4">
@@ -1957,41 +1957,41 @@
       <c r="H4">
         <v>-0.96</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="38">
         <v>11.08</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="28">
         <v>22.21</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="33">
         <v>34.45</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="29">
         <v>21.05</v>
       </c>
       <c r="M4" s="31">
         <v>8.95</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="30">
         <v>4.17</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="34">
         <v>0.7</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="39">
         <v>1.99</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="35">
         <v>-0.46</v>
       </c>
       <c r="R4" s="36">
         <v>-1.99</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="37">
         <v>-2.46</v>
       </c>
-      <c r="T4" s="39">
-        <v>-5.19</v>
+      <c r="T4" s="27">
+        <v>-4.4</v>
       </c>
     </row>
     <row r="5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>4.64</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="51">
         <v>5.12</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="48">
         <v>-5.38</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="44">
         <v>-9.79</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="52">
         <v>-8.54</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="49">
         <v>-12.18</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="40">
         <v>-15.6</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="41">
         <v>-18.85</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="46">
         <v>-17.8</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="42">
         <v>-17.2</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="50">
         <v>-18.47</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="47">
         <v>-17.05</v>
       </c>
-      <c r="T5" s="47">
-        <v>-23.81</v>
+      <c r="T5" s="43">
+        <v>-22.84</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>002865</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="65" t="str">
         <v>净买: 1604.62万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>-9.87</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="63">
         <v>-0.15</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="55">
         <v>-5.03</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="56">
         <v>-5.69</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="57">
         <v>-4.56</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="60">
         <v>-6.32</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="53">
         <v>-9.04</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="61">
         <v>-13.12</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="62">
         <v>-16.35</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="64">
         <v>-16.35</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="58">
         <v>-17.98</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="59">
         <v>-9.78</v>
       </c>
       <c r="T6" s="54">
-        <v>-27.88</v>
+        <v>-24.09</v>
       </c>
     </row>
     <row r="7">
@@ -2177,37 +2177,37 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="69">
+      <c r="I8" s="66">
         <v>80</v>
       </c>
-      <c r="J8" s="70">
+      <c r="J8" s="74">
         <v>60</v>
       </c>
-      <c r="K8" s="73">
+      <c r="K8" s="75">
         <v>60</v>
       </c>
-      <c r="L8" s="71">
+      <c r="L8" s="72">
         <v>60</v>
       </c>
-      <c r="M8" s="74">
+      <c r="M8" s="67">
         <v>60</v>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="73">
         <v>60</v>
       </c>
-      <c r="O8" s="75">
+      <c r="O8" s="76">
         <v>60</v>
       </c>
-      <c r="P8" s="66">
+      <c r="P8" s="68">
         <v>60</v>
       </c>
-      <c r="Q8" s="67">
+      <c r="Q8" s="69">
         <v>40</v>
       </c>
-      <c r="R8" s="68">
+      <c r="R8" s="70">
         <v>40</v>
       </c>
-      <c r="S8" s="76">
+      <c r="S8" s="71">
         <v>40</v>
       </c>
       <c r="T8" s="77">
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="84">
+      <c r="I9" s="83">
         <v>6.41</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="86">
         <v>4.44</v>
       </c>
-      <c r="K9" s="89">
+      <c r="K9" s="87">
         <v>6.73</v>
       </c>
-      <c r="L9" s="85">
+      <c r="L9" s="84">
         <v>4.29</v>
       </c>
       <c r="M9" s="78">
         <v>0.24</v>
       </c>
-      <c r="N9" s="79">
+      <c r="N9" s="88">
         <v>-3.19</v>
       </c>
-      <c r="O9" s="86">
+      <c r="O9" s="79">
         <v>-4.83</v>
       </c>
       <c r="P9" s="80">
         <v>-4.91</v>
       </c>
-      <c r="Q9" s="82">
+      <c r="Q9" s="85">
         <v>-5.88</v>
       </c>
-      <c r="R9" s="81">
+      <c r="R9" s="82">
         <v>-6.83</v>
       </c>
-      <c r="S9" s="83">
+      <c r="S9" s="89">
         <v>-5.14</v>
       </c>
-      <c r="T9" s="87">
-        <v>22.35</v>
+      <c r="T9" s="81">
+        <v>25.36</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/华鑫宁波分/index.xlsx
+++ b/youzi/华鑫宁波分/index.xlsx
@@ -39,13 +39,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,31 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
+        <fgColor rgb="FFE46874"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,13 +117,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
+        <fgColor rgb="FFE3626E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,55 +129,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,31 +285,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,72 +435,90 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -285,289 +531,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="7" t="str">
         <v>净卖: -1841.46万</v>
       </c>
       <c r="E2">
@@ -1833,28 +1833,28 @@
       <c r="H2">
         <v>0.21</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="13">
         <v>9.78</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="10">
         <v>4.55</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="8">
         <v>10.25</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="3">
         <v>8.54</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="9">
         <v>9.42</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="1">
         <v>3.67</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="11">
         <v>3.88</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="12">
         <v>3.73</v>
       </c>
       <c r="Q2" s="4">
@@ -1863,11 +1863,11 @@
       <c r="R2" s="5">
         <v>3.26</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="2">
         <v>0.88</v>
       </c>
-      <c r="T2" s="12">
-        <v>35.61</v>
+      <c r="T2" s="6">
+        <v>34.58</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002281</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -4437.11万</v>
       </c>
       <c r="E3">
@@ -1895,31 +1895,31 @@
       <c r="H3">
         <v>3.56</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="24">
         <v>6.22</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="25">
         <v>5.86</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="16">
         <v>4.44</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="26">
         <v>4.95</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="22">
         <v>1.33</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="23">
         <v>0.83</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="17">
         <v>3.23</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="14">
         <v>3.88</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="18">
         <v>1.66</v>
       </c>
       <c r="R3" s="19">
@@ -1928,8 +1928,8 @@
       <c r="S3" s="20">
         <v>2.73</v>
       </c>
-      <c r="T3" s="14">
-        <v>142.53</v>
+      <c r="T3" s="15">
+        <v>146.04</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>001209</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="29" t="str">
         <v>净买: 927.43万</v>
       </c>
       <c r="E4">
@@ -1957,41 +1957,41 @@
       <c r="H4">
         <v>-0.96</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="30">
         <v>11.08</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="27">
         <v>22.21</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="28">
         <v>34.45</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="37">
         <v>21.05</v>
       </c>
       <c r="M4" s="31">
         <v>8.95</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="32">
         <v>4.17</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="38">
         <v>0.7</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="35">
         <v>1.99</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="39">
         <v>-0.46</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="33">
         <v>-1.99</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="34">
         <v>-2.46</v>
       </c>
-      <c r="T4" s="27">
-        <v>-4.4</v>
+      <c r="T4" s="36">
+        <v>-3.48</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>001277</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="41" t="str">
         <v>净卖: -115.58万</v>
       </c>
       <c r="E5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>4.64</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="47">
         <v>5.12</v>
       </c>
       <c r="J5" s="48">
         <v>-5.38</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="42">
         <v>-9.79</v>
       </c>
       <c r="L5" s="52">
         <v>-8.54</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="43">
         <v>-12.18</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="49">
         <v>-15.6</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="44">
         <v>-18.85</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="50">
         <v>-17.8</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="45">
         <v>-17.2</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="46">
         <v>-18.47</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="51">
         <v>-17.05</v>
       </c>
-      <c r="T5" s="43">
-        <v>-22.84</v>
+      <c r="T5" s="40">
+        <v>-22.92</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>002865</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="64" t="str">
         <v>净买: 1604.62万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>-9.87</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="65">
         <v>-0.15</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="63">
         <v>-5.03</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="57">
         <v>-5.69</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="60">
         <v>-4.56</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="53">
         <v>-6.32</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="58">
         <v>-9.04</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="54">
         <v>-13.12</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="55">
         <v>-16.35</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="59">
         <v>-16.35</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="56">
         <v>-17.98</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="61">
         <v>-9.78</v>
       </c>
-      <c r="T6" s="54">
-        <v>-24.09</v>
+      <c r="T6" s="62">
+        <v>-21.12</v>
       </c>
     </row>
     <row r="7">
@@ -2180,37 +2180,37 @@
       <c r="I8" s="66">
         <v>80</v>
       </c>
-      <c r="J8" s="74">
+      <c r="J8" s="67">
         <v>60</v>
       </c>
-      <c r="K8" s="75">
+      <c r="K8" s="74">
         <v>60</v>
       </c>
-      <c r="L8" s="72">
+      <c r="L8" s="68">
         <v>60</v>
       </c>
-      <c r="M8" s="67">
+      <c r="M8" s="70">
         <v>60</v>
       </c>
-      <c r="N8" s="73">
+      <c r="N8" s="75">
         <v>60</v>
       </c>
       <c r="O8" s="76">
         <v>60</v>
       </c>
-      <c r="P8" s="68">
+      <c r="P8" s="71">
         <v>60</v>
       </c>
-      <c r="Q8" s="69">
+      <c r="Q8" s="72">
         <v>40</v>
       </c>
-      <c r="R8" s="70">
+      <c r="R8" s="69">
         <v>40</v>
       </c>
-      <c r="S8" s="71">
+      <c r="S8" s="77">
         <v>40</v>
       </c>
-      <c r="T8" s="77">
+      <c r="T8" s="73">
         <v>40</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="83">
+      <c r="I9" s="79">
         <v>6.41</v>
       </c>
-      <c r="J9" s="86">
+      <c r="J9" s="80">
         <v>4.44</v>
       </c>
-      <c r="K9" s="87">
+      <c r="K9" s="85">
         <v>6.73</v>
       </c>
-      <c r="L9" s="84">
+      <c r="L9" s="83">
         <v>4.29</v>
       </c>
-      <c r="M9" s="78">
+      <c r="M9" s="86">
         <v>0.24</v>
       </c>
-      <c r="N9" s="88">
+      <c r="N9" s="89">
         <v>-3.19</v>
       </c>
-      <c r="O9" s="79">
+      <c r="O9" s="84">
         <v>-4.83</v>
       </c>
-      <c r="P9" s="80">
+      <c r="P9" s="87">
         <v>-4.91</v>
       </c>
-      <c r="Q9" s="85">
+      <c r="Q9" s="81">
         <v>-5.88</v>
       </c>
       <c r="R9" s="82">
         <v>-6.83</v>
       </c>
-      <c r="S9" s="89">
+      <c r="S9" s="88">
         <v>-5.14</v>
       </c>
-      <c r="T9" s="81">
-        <v>25.36</v>
+      <c r="T9" s="78">
+        <v>26.62</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/华鑫宁波分/index.xlsx
+++ b/youzi/华鑫宁波分/index.xlsx
@@ -39,25 +39,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE56A76"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
+        <fgColor rgb="FFE46874"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,19 +105,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,19 +183,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
+        <fgColor rgb="FFF3BBC1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,31 +195,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,31 +327,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,13 +447,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,37 +531,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,313 +549,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="7" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -1841.46万</v>
       </c>
       <c r="E2">
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>0.21</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="12">
         <v>9.78</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="4">
         <v>4.55</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="13">
         <v>10.25</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="1">
         <v>8.54</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="2">
         <v>9.42</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="7">
         <v>3.67</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="5">
         <v>3.88</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="8">
         <v>3.73</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="3">
         <v>2.95</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="9">
         <v>3.26</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="6">
         <v>0.88</v>
       </c>
-      <c r="T2" s="6">
-        <v>34.58</v>
+      <c r="T2" s="10">
+        <v>22.26</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002281</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -4437.11万</v>
       </c>
       <c r="E3">
@@ -1895,41 +1895,41 @@
       <c r="H3">
         <v>3.56</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="22">
         <v>6.22</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="14">
         <v>5.86</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="23">
         <v>4.44</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="15">
         <v>4.95</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="18">
         <v>1.33</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="19">
         <v>0.83</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="20">
         <v>3.23</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="24">
         <v>3.88</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="25">
         <v>1.66</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="21">
         <v>1.05</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="16">
         <v>2.73</v>
       </c>
-      <c r="T3" s="15">
-        <v>146.04</v>
+      <c r="T3" s="26">
+        <v>160</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>001209</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="38" t="str">
         <v>净买: 927.43万</v>
       </c>
       <c r="E4">
@@ -1960,38 +1960,38 @@
       <c r="I4" s="30">
         <v>11.08</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="33">
         <v>22.21</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="36">
         <v>34.45</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="34">
         <v>21.05</v>
       </c>
       <c r="M4" s="31">
         <v>8.95</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="37">
         <v>4.17</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="39">
         <v>0.7</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="27">
         <v>1.99</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="28">
         <v>-0.46</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="29">
         <v>-1.99</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="32">
         <v>-2.46</v>
       </c>
-      <c r="T4" s="36">
-        <v>-3.48</v>
+      <c r="T4" s="35">
+        <v>-3.71</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>001277</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="48" t="str">
         <v>净卖: -115.58万</v>
       </c>
       <c r="E5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>4.64</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="51">
         <v>5.12</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="49">
         <v>-5.38</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="52">
         <v>-9.79</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="45">
         <v>-8.54</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="40">
         <v>-12.18</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="41">
         <v>-15.6</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="42">
         <v>-18.85</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5" s="43">
         <v>-17.8</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="46">
         <v>-17.2</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="44">
         <v>-18.47</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="50">
         <v>-17.05</v>
       </c>
-      <c r="T5" s="40">
-        <v>-22.92</v>
+      <c r="T5" s="47">
+        <v>-24.47</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>002865</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="65" t="str">
         <v>净买: 1604.62万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>-9.87</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="53">
         <v>-0.15</v>
       </c>
-      <c r="J6" s="63">
+      <c r="J6" s="54">
         <v>-5.03</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="58">
         <v>-5.69</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="61">
         <v>-4.56</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="55">
         <v>-6.32</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="62">
         <v>-9.04</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="63">
         <v>-13.12</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="56">
         <v>-16.35</v>
       </c>
       <c r="Q6" s="59">
         <v>-16.35</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="60">
         <v>-17.98</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="57">
         <v>-9.78</v>
       </c>
-      <c r="T6" s="62">
-        <v>-21.12</v>
+      <c r="T6" s="64">
+        <v>-27.32</v>
       </c>
     </row>
     <row r="7">
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="66">
+      <c r="I8" s="68">
         <v>80</v>
       </c>
-      <c r="J8" s="67">
+      <c r="J8" s="74">
         <v>60</v>
       </c>
-      <c r="K8" s="74">
+      <c r="K8" s="69">
         <v>60</v>
       </c>
-      <c r="L8" s="68">
+      <c r="L8" s="75">
         <v>60</v>
       </c>
-      <c r="M8" s="70">
+      <c r="M8" s="77">
         <v>60</v>
       </c>
-      <c r="N8" s="75">
+      <c r="N8" s="73">
         <v>60</v>
       </c>
-      <c r="O8" s="76">
+      <c r="O8" s="70">
         <v>60</v>
       </c>
-      <c r="P8" s="71">
+      <c r="P8" s="66">
         <v>60</v>
       </c>
-      <c r="Q8" s="72">
+      <c r="Q8" s="71">
         <v>40</v>
       </c>
-      <c r="R8" s="69">
+      <c r="R8" s="72">
         <v>40</v>
       </c>
-      <c r="S8" s="77">
+      <c r="S8" s="67">
         <v>40</v>
       </c>
-      <c r="T8" s="73">
+      <c r="T8" s="76">
         <v>40</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="79">
+      <c r="I9" s="87">
         <v>6.41</v>
       </c>
-      <c r="J9" s="80">
+      <c r="J9" s="88">
         <v>4.44</v>
       </c>
       <c r="K9" s="85">
         <v>6.73</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="78">
         <v>4.29</v>
       </c>
-      <c r="M9" s="86">
+      <c r="M9" s="83">
         <v>0.24</v>
       </c>
-      <c r="N9" s="89">
+      <c r="N9" s="86">
         <v>-3.19</v>
       </c>
       <c r="O9" s="84">
         <v>-4.83</v>
       </c>
-      <c r="P9" s="87">
+      <c r="P9" s="89">
         <v>-4.91</v>
       </c>
-      <c r="Q9" s="81">
+      <c r="Q9" s="79">
         <v>-5.88</v>
       </c>
-      <c r="R9" s="82">
+      <c r="R9" s="80">
         <v>-6.83</v>
       </c>
-      <c r="S9" s="88">
+      <c r="S9" s="81">
         <v>-5.14</v>
       </c>
-      <c r="T9" s="78">
-        <v>26.62</v>
+      <c r="T9" s="82">
+        <v>25.35</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/华鑫宁波分/index.xlsx
+++ b/youzi/华鑫宁波分/index.xlsx
@@ -45,54 +45,90 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAD1F2D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEA8791"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDF4755"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE3626E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -105,7 +141,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,19 +201,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,49 +321,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,19 +435,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,18 +537,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -243,36 +549,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -285,289 +567,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="10" t="str">
         <v>净卖: -1841.46万</v>
       </c>
       <c r="E2">
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>0.21</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="8">
         <v>9.78</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="11">
         <v>4.55</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="12">
         <v>10.25</v>
       </c>
       <c r="L2" s="1">
         <v>8.54</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="4">
         <v>9.42</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="2">
         <v>3.67</v>
       </c>
       <c r="O2" s="5">
         <v>3.88</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="9">
         <v>3.73</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="6">
         <v>2.95</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="13">
         <v>3.26</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="3">
         <v>0.88</v>
       </c>
-      <c r="T2" s="10">
-        <v>22.26</v>
+      <c r="T2" s="7">
+        <v>22.67</v>
       </c>
     </row>
     <row r="3">
@@ -1895,41 +1895,41 @@
       <c r="H3">
         <v>3.56</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="14">
         <v>6.22</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="22">
         <v>5.86</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="18">
         <v>4.44</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="19">
         <v>4.95</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="23">
         <v>1.33</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="24">
         <v>0.83</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="25">
         <v>3.23</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="15">
         <v>3.88</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="20">
         <v>1.66</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="26">
         <v>1.05</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="21">
         <v>2.73</v>
       </c>
-      <c r="T3" s="26">
-        <v>160</v>
+      <c r="T3" s="16">
+        <v>171.76</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>001209</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="36" t="str">
         <v>净买: 927.43万</v>
       </c>
       <c r="E4">
@@ -1957,41 +1957,41 @@
       <c r="H4">
         <v>-0.96</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="32">
         <v>11.08</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="37">
         <v>22.21</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="33">
         <v>34.45</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="27">
         <v>21.05</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="34">
         <v>8.95</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="38">
         <v>4.17</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="35">
         <v>0.7</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="29">
         <v>1.99</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="39">
         <v>-0.46</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="28">
         <v>-1.99</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="30">
         <v>-2.46</v>
       </c>
-      <c r="T4" s="35">
-        <v>-3.71</v>
+      <c r="T4" s="31">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>001277</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="47" t="str">
         <v>净卖: -115.58万</v>
       </c>
       <c r="E5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>4.64</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="46">
         <v>5.12</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="48">
         <v>-5.38</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="49">
         <v>-9.79</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="50">
         <v>-8.54</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="43">
         <v>-12.18</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="44">
         <v>-15.6</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="40">
         <v>-18.85</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="51">
         <v>-17.8</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="52">
         <v>-17.2</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="41">
         <v>-18.47</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="45">
         <v>-17.05</v>
       </c>
-      <c r="T5" s="47">
-        <v>-24.47</v>
+      <c r="T5" s="42">
+        <v>-22.56</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>002865</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="61" t="str">
         <v>净买: 1604.62万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>-9.87</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="62">
         <v>-0.15</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="53">
         <v>-5.03</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="63">
         <v>-5.69</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="64">
         <v>-4.56</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="56">
         <v>-6.32</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="58">
         <v>-9.04</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="59">
         <v>-13.12</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="54">
         <v>-16.35</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="55">
         <v>-16.35</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="65">
         <v>-17.98</v>
       </c>
       <c r="S6" s="57">
         <v>-9.78</v>
       </c>
-      <c r="T6" s="64">
-        <v>-27.32</v>
+      <c r="T6" s="60">
+        <v>-27.48</v>
       </c>
     </row>
     <row r="7">
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="68">
+      <c r="I8" s="66">
         <v>80</v>
       </c>
       <c r="J8" s="74">
         <v>60</v>
       </c>
-      <c r="K8" s="69">
+      <c r="K8" s="72">
         <v>60</v>
       </c>
-      <c r="L8" s="75">
+      <c r="L8" s="69">
         <v>60</v>
       </c>
-      <c r="M8" s="77">
+      <c r="M8" s="73">
         <v>60</v>
       </c>
-      <c r="N8" s="73">
+      <c r="N8" s="75">
         <v>60</v>
       </c>
-      <c r="O8" s="70">
+      <c r="O8" s="67">
         <v>60</v>
       </c>
-      <c r="P8" s="66">
+      <c r="P8" s="68">
         <v>60</v>
       </c>
-      <c r="Q8" s="71">
+      <c r="Q8" s="70">
         <v>40</v>
       </c>
-      <c r="R8" s="72">
+      <c r="R8" s="76">
         <v>40</v>
       </c>
-      <c r="S8" s="67">
+      <c r="S8" s="77">
         <v>40</v>
       </c>
-      <c r="T8" s="76">
+      <c r="T8" s="71">
         <v>40</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="87">
+      <c r="I9" s="85">
         <v>6.41</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="86">
         <v>4.44</v>
       </c>
-      <c r="K9" s="85">
+      <c r="K9" s="89">
         <v>6.73</v>
       </c>
-      <c r="L9" s="78">
+      <c r="L9" s="84">
         <v>4.29</v>
       </c>
-      <c r="M9" s="83">
+      <c r="M9" s="78">
         <v>0.24</v>
       </c>
-      <c r="N9" s="86">
+      <c r="N9" s="79">
         <v>-3.19</v>
       </c>
-      <c r="O9" s="84">
+      <c r="O9" s="87">
         <v>-4.83</v>
       </c>
-      <c r="P9" s="89">
+      <c r="P9" s="88">
         <v>-4.91</v>
       </c>
-      <c r="Q9" s="79">
+      <c r="Q9" s="80">
         <v>-5.88</v>
       </c>
-      <c r="R9" s="80">
+      <c r="R9" s="81">
         <v>-6.83</v>
       </c>
-      <c r="S9" s="81">
+      <c r="S9" s="82">
         <v>-5.14</v>
       </c>
-      <c r="T9" s="82">
-        <v>25.35</v>
+      <c r="T9" s="83">
+        <v>28.24</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/华鑫宁波分/index.xlsx
+++ b/youzi/华鑫宁波分/index.xlsx
@@ -39,25 +39,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB62431"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,7 +141,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,13 +207,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC482"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,7 +309,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,19 +459,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626E"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,139 +507,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DDE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF6ED"/>
+        <fgColor rgb="FF1F8337"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,6 +525,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -286,258 +538,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002130</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="13" t="str">
         <v>净卖: -1841.46万</v>
       </c>
       <c r="E2">
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>0.21</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="1">
         <v>9.78</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="8">
         <v>4.55</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="9">
         <v>10.25</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="10">
         <v>8.54</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="5">
         <v>9.42</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="6">
         <v>3.67</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="7">
         <v>3.88</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="2">
         <v>3.73</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="3">
         <v>2.95</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="11">
         <v>3.26</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="4">
         <v>0.88</v>
       </c>
-      <c r="T2" s="7">
-        <v>22.67</v>
+      <c r="T2" s="12">
+        <v>18.32</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002281</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="15" t="str">
         <v>净卖: -4437.11万</v>
       </c>
       <c r="E3">
@@ -1895,41 +1895,41 @@
       <c r="H3">
         <v>3.56</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="22">
         <v>6.22</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="20">
         <v>5.86</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="23">
         <v>4.44</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="26">
         <v>4.95</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="24">
         <v>1.33</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="21">
         <v>0.83</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="16">
         <v>3.23</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="17">
         <v>3.88</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="18">
         <v>1.66</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="19">
         <v>1.05</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="25">
         <v>2.73</v>
       </c>
-      <c r="T3" s="16">
-        <v>171.76</v>
+      <c r="T3" s="14">
+        <v>176.77</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>001209</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 927.43万</v>
       </c>
       <c r="E4">
@@ -1957,41 +1957,41 @@
       <c r="H4">
         <v>-0.96</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="33">
         <v>11.08</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="38">
         <v>22.21</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="28">
         <v>34.45</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="39">
         <v>21.05</v>
       </c>
       <c r="M4" s="34">
         <v>8.95</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="27">
         <v>4.17</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="30">
         <v>0.7</v>
       </c>
       <c r="P4" s="29">
         <v>1.99</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="35">
         <v>-0.46</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="31">
         <v>-1.99</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="36">
         <v>-2.46</v>
       </c>
-      <c r="T4" s="31">
-        <v>-3.2</v>
+      <c r="T4" s="37">
+        <v>-3.34</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>001277</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="45" t="str">
         <v>净卖: -115.58万</v>
       </c>
       <c r="E5">
@@ -2022,38 +2022,38 @@
       <c r="I5" s="46">
         <v>5.12</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="47">
         <v>-5.38</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="48">
         <v>-9.79</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="43">
         <v>-8.54</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="52">
         <v>-12.18</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="40">
         <v>-15.6</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="49">
         <v>-18.85</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="41">
         <v>-17.8</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="42">
         <v>-17.2</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="44">
         <v>-18.47</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="50">
         <v>-17.05</v>
       </c>
-      <c r="T5" s="42">
-        <v>-22.56</v>
+      <c r="T5" s="51">
+        <v>-22.79</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>002865</v>
       </c>
-      <c r="D6" s="61" t="str">
+      <c r="D6" s="65" t="str">
         <v>净买: 1604.62万</v>
       </c>
       <c r="E6">
@@ -2087,35 +2087,35 @@
       <c r="J6" s="53">
         <v>-5.03</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="57">
         <v>-5.69</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="54">
         <v>-4.56</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="60">
         <v>-6.32</v>
       </c>
       <c r="N6" s="58">
         <v>-9.04</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="55">
         <v>-13.12</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="63">
         <v>-16.35</v>
       </c>
-      <c r="Q6" s="55">
+      <c r="Q6" s="64">
         <v>-16.35</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="59">
         <v>-17.98</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="56">
         <v>-9.78</v>
       </c>
-      <c r="T6" s="60">
-        <v>-27.48</v>
+      <c r="T6" s="61">
+        <v>-29.26</v>
       </c>
     </row>
     <row r="7">
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="66">
+      <c r="I8" s="70">
         <v>80</v>
       </c>
-      <c r="J8" s="74">
+      <c r="J8" s="66">
         <v>60</v>
       </c>
-      <c r="K8" s="72">
+      <c r="K8" s="74">
         <v>60</v>
       </c>
-      <c r="L8" s="69">
+      <c r="L8" s="75">
         <v>60</v>
       </c>
-      <c r="M8" s="73">
+      <c r="M8" s="71">
         <v>60</v>
       </c>
-      <c r="N8" s="75">
+      <c r="N8" s="67">
         <v>60</v>
       </c>
-      <c r="O8" s="67">
+      <c r="O8" s="68">
         <v>60</v>
       </c>
-      <c r="P8" s="68">
+      <c r="P8" s="76">
         <v>60</v>
       </c>
-      <c r="Q8" s="70">
+      <c r="Q8" s="69">
         <v>40</v>
       </c>
-      <c r="R8" s="76">
+      <c r="R8" s="72">
         <v>40</v>
       </c>
       <c r="S8" s="77">
         <v>40</v>
       </c>
-      <c r="T8" s="71">
+      <c r="T8" s="73">
         <v>40</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="85">
+      <c r="I9" s="86">
         <v>6.41</v>
       </c>
-      <c r="J9" s="86">
+      <c r="J9" s="89">
         <v>4.44</v>
       </c>
-      <c r="K9" s="89">
+      <c r="K9" s="78">
         <v>6.73</v>
       </c>
-      <c r="L9" s="84">
+      <c r="L9" s="79">
         <v>4.29</v>
       </c>
-      <c r="M9" s="78">
+      <c r="M9" s="82">
         <v>0.24</v>
       </c>
-      <c r="N9" s="79">
+      <c r="N9" s="80">
         <v>-3.19</v>
       </c>
-      <c r="O9" s="87">
+      <c r="O9" s="81">
         <v>-4.83</v>
       </c>
-      <c r="P9" s="88">
+      <c r="P9" s="87">
         <v>-4.91</v>
       </c>
-      <c r="Q9" s="80">
+      <c r="Q9" s="83">
         <v>-5.88</v>
       </c>
-      <c r="R9" s="81">
+      <c r="R9" s="84">
         <v>-6.83</v>
       </c>
-      <c r="S9" s="82">
+      <c r="S9" s="88">
         <v>-5.14</v>
       </c>
-      <c r="T9" s="83">
-        <v>28.24</v>
+      <c r="T9" s="85">
+        <v>27.94</v>
       </c>
     </row>
   </sheetData>
